--- a/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
+++ b/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
@@ -561,7 +561,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月6日。</t>
+          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月7日。</t>
         </is>
       </c>
     </row>
@@ -682,10 +682,10 @@
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>・完了していない確認事項は161件あります。そのまま並べると一覧として用をなさないため、02シートは「確認先が広域連合であり、影響度の点が4点以上のもの」に絞って18件を掲げています（絞り込みの条件は本欄のとおりです）。
-・03シートは確認先に構成町を含むもの36件です（町別11件・3町共通25件）。
+          <t>・完了していない確認事項は164件あります。そのまま並べると一覧として用をなさないため、02シートは「確認先が広域連合であり、影響度の点が4点以上のもの」に絞って18件を掲げています（絞り込みの条件は本欄のとおりです）。
+・03シートは確認先に構成町を含むもの37件です（町別11件・3町共通26件）。
 ・影響度の点は、期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで付けています。付け方は別冊「日次の状況と翌日の作業順位」と同じです。
-・決まらない場合の当方の扱い（仮置き）は161件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
+・決まらない場合の当方の扱い（仮置き）は164件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1694,7 +1694,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認先に構成町を含む確認事項36件（町別11件・3町共通25件）と、町からご提供をお願いする資料4件です。町別は町ごとに、3町共通は点の高い順に並べています。</t>
+          <t>確認先に構成町を含む確認事項37件（町別11件・3町共通26件）と、町からご提供をお願いする資料4件です。町別は町ごとに、3町共通は点の高い順に並べています。</t>
         </is>
       </c>
     </row>
@@ -2793,160 +2793,188 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="46" ht="46" customHeight="1">
+      <c r="A46" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>の当方の扱い＝国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>3　町からご提供をお願いする資料</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>入手先</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>希望時期</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>何が確定するか</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="46" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>3町</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
     </row>
     <row r="50" ht="46" customHeight="1">
       <c r="A50" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>総務省・3町</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>公表後</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>世帯構成の現状</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
     </row>
     <row r="51" ht="46" customHeight="1">
       <c r="A51" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>総務省・3町</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>公表後</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>世帯構成の現状</t>
         </is>
       </c>
     </row>
     <row r="52" ht="46" customHeight="1">
       <c r="A52" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>事業所・施設の定員と稼働の実績</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="46" customHeight="1">
+      <c r="A53" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B53" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>美瑛町・3町</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="48" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54" ht="48" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>注）資料のご提供がない場合は、現に確認できている値で確定し、出所と制約を計画本文の注記に書く扱いとしています。算定そのものが止まるものはありません。</t>
         </is>
@@ -2955,12 +2983,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A54:F54"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A48:F48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4128,7 +4156,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>No.1〜No.174／174件／重複 なし</t>
+          <t>No.1〜No.177／177件／重複 なし</t>
         </is>
       </c>
       <c r="E5" s="17" t="inlineStr">
@@ -4153,7 +4181,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>未決161件／仮置きのないもの なし</t>
+          <t>未決164件／仮置きのないもの なし</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">

--- a/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
+++ b/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
@@ -8,12 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_この打合せについて" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_先に申し上げること" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_事前に決めていただきたいこと" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_ヒアリングで3町へ伺うこと" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_月額を動かす前提" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_ヒアリングの進め方" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_自己点検" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_最低限の確認事項と時間配分" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_先に申し上げること" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_事前に決めていただきたいこと" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_ヒアリングで3町へ伺うこと" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_月額を動かす前提" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_ヒアリングの進め方" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_自己点検" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -102,7 +103,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -124,11 +125,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -147,17 +192,34 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
@@ -170,9 +232,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -542,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -597,17 +656,17 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>ヒアリングに入る前に広域連合で決めていただくこと</t>
+          <t>最低限の確認事項と時間配分</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>3町へ伺う内容は、広域連合としての置き方が決まっていないと問いが立たない。例えば必要利用定員総数の基盤整備単位が決まらないと、各町へ整備の方針を伺うことができない</t>
+          <t>打合せが1〜2時間であるため、この場で決めるものをA群5件に絞り、所要の目安を分で付した。90分の場合と120分の場合の時間配分の案を置く</t>
         </is>
       </c>
     </row>
@@ -617,7 +676,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>3町へ伺うことの最終確認</t>
+          <t>ヒアリングに入る前に広域連合で決めていただくこと</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -627,7 +686,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>町別の論点と3町共通の論点を、伺う相手と順序を含めて確かめる。町からご提供をお願いする資料もここで確かめる</t>
+          <t>3町へ伺う内容は、広域連合としての置き方が決まっていないと問いが立たない。例えば必要利用定員総数の基盤整備単位が決まらないと、各町へ整備の方針を伺うことができない</t>
         </is>
       </c>
     </row>
@@ -637,7 +696,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>保険料の月額を動かす前提の共有</t>
+          <t>3町へ伺うことの最終確認</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -647,7 +706,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>仮置きのまま算定しているものを示す。ヒアリングの場で町から整備の意向が示されると見込量が動くため、どこまでが動き得るのかを先に共有する</t>
+          <t>町別の論点と3町共通の論点を、伺う相手と順序を含めて確かめる。町からご提供をお願いする資料もここで確かめる</t>
         </is>
       </c>
     </row>
@@ -657,33 +716,54 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
+          <t>保険料の月額を動かす前提の共有</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>仮置きのまま算定しているものを示す。ヒアリングの場で町から整備の意向が示されると見込量が動くため、どこまでが動き得るのかを先に共有する</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
           <t>ヒアリングの進め方</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>日程・配付する資料・記録の様式・ヒアリング後の工程を確かめる</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="11"/>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>2　掲げる範囲</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>・完了していない確認事項は164件あります。そのまま並べると一覧として用をなさないため、02シートは「確認先が広域連合であり、影響度の点が4点以上のもの」に絞って18件を掲げています（絞り込みの条件は本欄のとおりです）。
-・03シートは確認先に構成町を含むもの37件です（町別11件・3町共通26件）。
+    <row r="13" ht="180" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>・完了していない確認事項は164件あります。そのまま並べると一覧として用をなさないため、この場で決めるものは01シートのA群5件（計55分）に絞っています。
+・03シートは「確認先が広域連合であり、影響度の点が4点以上のもの」に絞って19件を掲げています（A群・B群に挙げたものは点が下限に届かなくても掲げています）。A群はこの中から選んでいます（03シートに含まれないものは確認先に構成町を含むものです）。
+・04シートは確認先に構成町を含むもの37件です（町別11件・3町共通26件）。
 ・影響度の点は、期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで付けています。付け方は別冊「日次の状況と翌日の作業順位」と同じです。
 ・決まらない場合の当方の扱い（仮置き）は164件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
         </is>
@@ -695,13 +775,912 @@
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>最低限ご確認いただきたい事項と優先順位</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>打合せの時間が1〜2時間であることを踏まえ、完了していない確認事項164件のうち、この場で決めるものをA群5件（計55分）に絞りました。B群4件（計20分）は時間があれば、残りは決まらない場合の当方の扱い（仮置き）のまま進めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　A群　この場で決めていただきたいこと（計55分）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>確認事項No.</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>決めること</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>なぜこの場で決めるか</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>観点</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>目安</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="96" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>No.88・No.113・No.84</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>日常生活圏域と必要利用定員総数（基盤整備の単位）</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>これが決まらないと、各町へ整備の方針を伺うことができません。計画素案の未確定箇所は第6章第4節（施設の見込み）に最も多く集中しており、基盤整備の単位が決まればその大半が解消します。法第117条第2項第1号の法定記載事項です。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>①③④</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>15分</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="96" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>No.137・No.104・No.109・No.110</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり給付費（単価）をどの年度で固定するか</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>月額への効きが最も大きい事項です（最大＋327円）。現在は令和7年度の実績で固定しており、令和8年度及び令和9年度の介護報酬改定と、実績として現れている単価の伸び（年率1.32％から1.75％）を見込んでいません。第2次概算の前提になります。</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>②④</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>15分</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="96" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>No.112・No.150</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業及び認知症総合支援事業の量の見込み</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>影響度の点が最も高い2件です。法第117条第2項第2号の法定記載事項であり、3町へどの資料をご依頼するかがここで決まります。3町の実施報告書で確認できた実施状況は単位が延べ人数・回数・食数で混在しており合計できないため、令和6年度の利用者実人数を据え置く扱いでよいかをお決めいただきたい。</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>①③④</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="96" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>No.152・No.153・No.174</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>人口の将来推計を案Cのままとするか</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>町別データシートで町別の将来推計をお示しするかに直結し、ヒアリングで配付する資料の作りが変わります。令和8年9月10日のご了承では、町別は現況のみを計画本文に加え、将来推計は3町計のままとしています。第1号被保険者数の系列が3つあるため、どれを正式に採るかも併せて要ります。</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>①④</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="96" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>No.106・No.107・No.105</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>サービス別の趨勢の補正と施策反映を行うか</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>第2次概算の前提になります。補正のみで月額▲58円、施設及び居住系を減らさない条件を加えると＋48円です。現在はいずれも安全側（保険料が不足する側に誤らない向き）に織り込まないまま置いています。</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>②④</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="96" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>注1）観点の記号は本シート3のとおりです。A群は4つの観点のうち2つ以上に当たるものとしました。
+注2）各件の「決まらない場合の当方の扱い（仮置き）」は03シート（広域連合で決まるもの）及び04シート（3町へ伺うもの）の表にあります。この場でご否認がなければ、そのまま第2次概算に用います。
+注3）A1は確認先に構成町を含みますが、基盤整備の単位をどう置くかは広域連合としての判断であり、これを先に決めないと各町へ整備の方針を伺えません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2　B群　時間があれば決めていただきたいこと（計20分）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>確認事項No.</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>決めること</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>この場で伺う理由</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>観点</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>目安</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="76" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>No.93・No.86</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>調整交付金の扱い（適正化の取組による減額・交付見込額の控除）</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月18日の社会保障審議会介護保険部会で、年齢区分の精緻化により交付額が増加する保険者が介護給付適正化の主要3事業のいずれかを実施していない場合に増加額の5％を減額することが示されました。当広域連合はケアプラン等の点検を実施していないため該当します。交付見込額を収納必要額から控除しない当方の扱いの確認も併せて。</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="76" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>No.131・No.114</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>計画本文の掲げ方（見込量の表・中長期推計）</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>既に計画素案へ反映している内容のご確認です。見込量の表に利用者数・利用回（日）数・給付費を掲げ、中長期推計は令和17年度・令和22年度を掲げています。</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="76" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>No.175</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>令和10年4月1日までに3町の介護保険事務システムの標準化対応とデータ移行を終えることが国から示されています。ヒアリングで3町へ伺う項目として加えるかをご確認いただきたい。</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>No.130</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>市町村認知症施策推進計画と意見の聴取</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>3町がそれぞれ市町村計画を策定する案Bで素案へ反映済みです。認知症の人及びその家族等からの意見の聴取の主体・方法・時期が残っています。</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>注）B群はいずれも既に計画素案へ反映している内容のご確認又はヒアリングで伺う項目に加えるかのご確認です。この場で決まらなくても第2次概算は組めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>3　A群に選んだ観点</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>観点</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>A群で当たるもの</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>ヒアリングの問いが立たない</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>広域連合としての置き方が決まらないと、各町へ伺う問いが立たない</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>A1・A3・A4</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>月額への効きが大きい</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>保険料の月額を100円以上動かし得る</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>A2・A5</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>法定記載事項に直結する</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>介護保険法第117条が定める記載事項そのものである</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>A1・A3</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>第2次概算の前提になる</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>令和8年10月30日に提示する算定の前提として要る</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>A1・A2・A3・A4・A5</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>注）4つの観点のうち1つだけに当たるものはB群又はC群としました。期限は観点に用いていません。期限が令和8年10月までのものが大半であり、期限だけでは順位が付かないためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>4　時間配分の案</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>枠</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>分</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>90分</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>冒頭　仮置きによる算定の結果と、低く出る側に寄っていること（02シート）</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="5" t="inlineStr"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>A群　この場で決めること（5件・01シート）</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>55分</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="5" t="inlineStr"/>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>3町へ伺う事項と順序の確認（04シート）</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>15分</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="5" t="inlineStr"/>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>ヒアリングの進め方（日程・配付資料・記録の様式。06シート）</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="5" t="inlineStr"/>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>予備</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="15" t="inlineStr"/>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>90分</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>120分</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>冒頭　仮置きによる算定の結果と、低く出る側に寄っていること（02シート）</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="5" t="inlineStr"/>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>A群　この場で決めること（5件・01シート）</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>55分</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="5" t="inlineStr"/>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>B群　時間があれば決めること（4件・01シート）</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>20分</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="5" t="inlineStr"/>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>3町へ伺う事項と順序の確認（04シート）</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>20分</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="5" t="inlineStr"/>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>ヒアリングの進め方（日程・配付資料・記録の様式。06シート）</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>15分</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="5" t="inlineStr"/>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>予備</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="15" t="inlineStr"/>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>120分</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="52" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>注1）90分の場合はB群を扱いません。B群は後日の持ち帰り又はメールでのご回答で足ります。
+注2）3町へ伺う事項と順序の確認（04シート）は、A群が決まってから行うことを想定しています（A群の置き方により伺う問いが変わるためです）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>5　C群　この場では扱わないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="130" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>・A群・B群に挙げた確認事項は実数21件です。残る143件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
+・このうち国の告示・公布を待つもの（据え置きの区分C）4件はこの場でお決めいただくことができません。介護報酬改定率・第1号被保険者負担割合・所得段階の政令改正・令和9年4月新設の3区分です。告示・公布の後に再算定します。
+・受託者の側で確定できるもの（区分A）は残っていません。令和8年10月1日に4件（要介護度別の単価・1人1月あたり利用回（日）数・要介護度の構成・季節補正）を確定しました。
+・仮置きのまま計画素案へ反映した事項は46件あります（別冊「3町合同意見交換会資料」第6節3に一覧があります）。いずれもご決定をお待ちしているものであり、ご否認があれば素案の側を改めます。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C35:E35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -765,7 +1744,7 @@
           <t>総給付費（第10期3か年計）</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>9,035,114,142円</t>
         </is>
@@ -785,7 +1764,7 @@
           <t>標準給付費見込額（A）</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>9,569,019,924円</t>
         </is>
@@ -805,7 +1784,7 @@
           <t>地域支援事業費（B）</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>531,483,777円</t>
         </is>
@@ -825,7 +1804,7 @@
           <t>保険料収納必要額（J）</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>2,088,171,801円</t>
         </is>
@@ -845,7 +1824,7 @@
           <t>補正後第1号被保険者数（3か年）</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>27,301.2人</t>
         </is>
@@ -865,7 +1844,7 @@
           <t>算定上の月額基準額</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>6,438.26円</t>
         </is>
@@ -877,20 +1856,20 @@
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>保険料基準額（百円未満四捨五入）</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>6,400円</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>第9期の基準額6,400円と同額になります</t>
         </is>
@@ -911,15 +1890,16 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="130" customHeight="1">
+    <row r="16" ht="170" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>単価を令和7年度の実績で固定しており、令和8年度及び令和9年度の介護報酬改定と、実績として現れている単価の伸びを見込んでいません。
 ・単価の実績の伸び（年率1.32％から1.75％）を織り込むと月額＋245円から＋327円
 ・介護報酬改定率1％あたり月額＋61円
 ・第1号被保険者負担割合が23％から24％になると月額約＋290円
+・調整交付金の減額（年齢区分の精緻化により交付額が増加する保険者が介護給付適正化の主要3事業のいずれかを実施していない場合に増加額の5％を減額。令和8年9月18日の社会保障審議会介護保険部会）。当広域連合はケアプラン等の点検を実施していないため該当しますが、増加額が示されていないため減額の額は算定できません
 一方、下向きに働くもの（介護給付適正化・サービス別の趨勢の補正・介護給付費準備基金の取崩し）はいずれも織り込んでいません。
-上向きは国の告示・公布により生じるもので、資料のご提供とは関わりなく動きます。下向きはご判断を要するものです。04シートに一覧があります。</t>
+上向きは国の告示・公布により生じるもので、資料のご提供とは関わりなく動きます。下向きはご判断を要するものです。05シートに一覧があります。</t>
         </is>
       </c>
     </row>
@@ -957,13 +1937,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -985,7 +1965,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認先が広域連合であり、影響度の点が4点以上のもの18件です。点の高い順に並べています。「決まらない場合の当方の扱い」は仮置きであり、この打合せでご否認がなければそのまま第2次概算に用います。</t>
+          <t>確認先が広域連合であり、影響度の点が4点以上のもの（及びA群・B群に挙げたもの）19件です。点の高い順に並べています。「決まらない場合の当方の扱い」は仮置きであり、この打合せでご否認がなければそのまま第2次概算に用います。</t>
         </is>
       </c>
     </row>
@@ -1050,7 +2030,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>最大7円</t>
         </is>
@@ -1085,7 +2065,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1120,7 +2100,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>最大47円</t>
         </is>
@@ -1155,7 +2135,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>最大58円</t>
         </is>
@@ -1189,7 +2169,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1223,7 +2203,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1258,7 +2238,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1293,7 +2273,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1328,7 +2308,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1362,7 +2342,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1396,7 +2376,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1429,7 +2409,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1463,7 +2443,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>最大13円</t>
         </is>
@@ -1497,7 +2477,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>最大327円</t>
         </is>
@@ -1532,7 +2512,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1566,7 +2546,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1600,7 +2580,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>最大327円</t>
         </is>
@@ -1634,7 +2614,7 @@
           <t>告示後</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>最大290円</t>
         </is>
@@ -1645,29 +2625,66 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="190" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>注1）この打合せで特にお決めいただきたいのは次の4件です。
-　①No.112・No.150　地域支援事業と認知症総合支援事業の量の見込み。法第117条第2項第2号の記載事項であり、3町の実施報告書で確認できた実施状況は単位が延べ人数・回数・食数で混在しているため合計できません。令和6年度の利用者実人数を据え置く扱いでよいかをお決めいただきたい。
-　②No.104・No.109・No.137　単価をどの年度で固定するか。月額への効きが最も大きい事項です（最大＋327円）。
-　③No.106　サービス別の趨勢を半分反映する補正を行うか（補正のみで月額▲58円、施設・居住系を減らさない条件を加えると＋48円）。
-　④No.152・No.153　人口の将来推計を案Cのままとするか。町別の推計を計画本文に掲げるかは、ヒアリングで町別の数値をお示しするかに直結します。
-注2）月額への効きの欄が「―」のものは、保険料には影響せず計画本文の記述に関わるものです。</t>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>174</v>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>人口推計コーホート分析の妥当性検証 07シート
+見える化へ入力する箇所と入力値 02シート
+計画素案 第2章第1節・第6章第1節</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>の当方の扱い＝案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="170" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>注1）この打合せで特にお決めいただきたいのは、01シートのA群5件（計55分）です。本シートの中では次のものが当たります。
+　A1　No.88・No.113・No.84　日常生活圏域と必要利用定員総数（基盤整備の単位）（15分）
+　A2　No.137・No.104・No.109・No.110　1人1月あたり給付費（単価）をどの年度で固定するか（15分）
+　A3　No.112・No.150　地域支援事業及び認知症総合支援事業の量の見込み（10分）
+　A4　No.152・No.153・No.174　人口の将来推計を案Cのままとするか（10分）
+　A5　No.106・No.107・No.105　サービス別の趨勢の補正と施策反映を行うか（5分）
+注2）月額への効きの欄が「―」のものは、保険料には影響せず計画本文の記述に関わるものです。
+注3）点が4点に届かないものも、A群・B群に挙げたものは本シートに掲げています。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2994,7 +4011,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3058,7 +4075,7 @@
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -3073,7 +4090,7 @@
           <t>令和7年度の実績単価で固定した。改定率を乗じた場合の感度をサービス見込量の算定に示した</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>改定率1％あたり月額＋61円。単価の年率1.32％から1.75％の伸びを見込まないことは月額＋245円〜＋327円に当たり、令和8年度の水準（残差＋1.63％）に置くと月額＋99円（確認事項No.104）</t>
         </is>
@@ -3088,7 +4105,7 @@
       <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3103,7 +4120,7 @@
           <t>取崩しを行わない（I＝0）</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>1億円の取崩しで月額約▲310円</t>
         </is>
@@ -3118,7 +4135,7 @@
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -3133,7 +4150,7 @@
           <t>第9期と同じ23％で置いた</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>1ポイントの違いで月額が約290円動く</t>
         </is>
@@ -3148,7 +4165,7 @@
       <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3178,7 +4195,7 @@
       <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3208,7 +4225,7 @@
       <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3238,7 +4255,7 @@
       <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3268,7 +4285,7 @@
       <c r="A12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3298,7 +4315,7 @@
       <c r="A13" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3328,7 +4345,7 @@
       <c r="A14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3358,7 +4375,7 @@
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3388,7 +4405,7 @@
       <c r="A16" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3418,7 +4435,7 @@
       <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3448,7 +4465,7 @@
       <c r="A18" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -3478,7 +4495,7 @@
       <c r="A19" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -3508,7 +4525,7 @@
       <c r="A20" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3538,7 +4555,7 @@
       <c r="A21" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3568,7 +4585,7 @@
       <c r="A22" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3598,7 +4615,7 @@
       <c r="A23" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3628,7 +4645,7 @@
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>注1）区分Bは広域連合・3町のご判断又は資料を待つもので、届かない場合は現に確認できている値で確定します。区分Cは国の告示・公布を待つもので、「受領できない」では済まないものです（公布後に再算定します）。
-注2）効きの欄の額は、本計画の算定の基礎で求めたものです。効きは、据え置きの一覧で名を挙げている確認事項に結び付けています。関係する確認事項が複数あるものは、代表の1件に額が付きます（02シートで「―」となっているものに効きがないという意味ではありません）。
+注2）効きの欄の額は、本計画の算定の基礎で求めたものです。効きは、据え置きの一覧で名を挙げている確認事項に結び付けています。関係する確認事項が複数あるものは、代表の1件に額が付きます（03シートで「―」となっているものに効きがないという意味ではありません）。
 介護報酬改定率を乗じることと単価の伸びを延ばすことを重ねると二重になります。
 注3）受託者の側で確定できるもの（区分A）は残っていません（令和8年10月1日に要介護度別の単価・1人1月あたり利用回（日）数・要介護度の構成・季節補正の4件を確定しました）。</t>
         </is>
@@ -3639,445 +4656,6 @@
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ヒアリングの進め方</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="58" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>日程・お持ちする資料・記録の様式・ヒアリング後の工程です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>1　日程</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>時期</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>場</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>令和8年10月8日</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>広域連合・受託者</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>事前打合せ。本資料の02シートの決定と、03シートの伺う事項・順序の確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>令和8年10月上旬</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>3町合同</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>意見交換会。3町共通の確認事項と地域課題。別冊「3町合同意見交換会資料」による</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>令和8年10月中旬から下旬</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>町ごと</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>町別ヒアリング。03シートの1の事項を町ごとに伺う</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>令和8年10月30日</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>広域連合</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>サービス見込量 第2次概算の提示</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>令和8年11月13日</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>広域連合</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>予算編成用の数値の提示</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>令和8年11月</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>広域連合・3町</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>3町の意見の反映と計画の骨子の整理</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2　お持ちする資料（いずれも既にお送りしているもの）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>資料</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>使う場面</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>別冊「3町ヒアリング資料」</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>ヒアリング本体</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>伺う事項と当方の整理を章立てで示したもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>別冊「キックオフ会議ヒアリングシート」</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>ヒアリング本体</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>伺った内容をその場で書き留める記録の用紙</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>別冊「3町別の論点整理」</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>ヒアリング本体</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>町ごとの現在地と論点、3町共通の論点、協議の進め方</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>別冊「10月 地域課題の整理と3町協議の確認事項」</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>ヒアリング本体</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>地域課題15件と、町ごとの確認事項（町別の3シート）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>別冊「町別データシート」</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>町へお示しするもの</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>町ごとの人口・認定者数・サービスの利用状況・総合事業</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>別冊「交付金 市町村分評価指標と3町の評価」</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>町へお示しするもの</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>評価指標の大項目と明細列ごとの3町の得点</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>別冊「交付金評価の取りまとめと第10期への反映」</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>町へお示しするもの</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>3か年の推移、全国との比較、一部の町のみ得点している項目</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>別冊「サービス見込量の算定_第2次概算」</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>協議の前提</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>第1次概算からの差分と、月額を動かす前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>別冊「資料を受領できない場合のサービス見込量」</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>協議の前提</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>資料のご提供がない場合に確定する値と、確定しない値</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="48" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>注）上記は「3町ヒアリング・打合せ資料一式」として束ねたものに収めています。索引に、どれをどの場面で開くかを1行ずつ付しています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>3　町別データシートをお示しする際の留意</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="130" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>・町別データシートの数値は計画作成支援ツールによるもので、3町を足しても広域連合の実績（介護保険事業状況報告）の値になりません。区域外の施設を利用する当連合の被保険者と、区域内の施設を利用する他の保険者の被保険者の扱いが違うためです（施設・居住系の月平均利用者数は3町計527人に対し保険者単位480.17人）。
-・サービス見込量・給付費・保険料は保険者（広域連合）を単位として算定するもので、町別には算定しません。町別に掲げるのは実績（人口・認定者数・給付費・事業所・総合事業・交付金の得点）です。
-・将来推計を町別に掲げるかは確認事項No.152のご判断によります（令和8年9月10日のご了承では、町別は現況のみを計画本文に加え、将来推計は3町計のままとしています）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>4　ヒアリングの場で踏み込まないこと</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="110" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>・保険料の額は3町計の概算までをお示しします。町別への按分は広域連合の規約によるものであり、当方に案はありません。
-・他の団体の名は協議の場に限ります。交付金の比較に用いている団体名は計画本文には掲げません。
-・得点が0である項目について、「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できません。評価調書によるご確認をお願いします。
-・第10期の施策に位置づけるかどうかは取組の必要性から判断するもので、交付金の得点のみを理由とはしません。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4089,7 +4667,466 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ヒアリングの進め方</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>日程・お持ちする資料・記録の様式・ヒアリング後の工程です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　日程</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>時期</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>場</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>令和8年10月8日</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>広域連合・受託者</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>事前打合せ。本資料の01シートのA群の決定と、04シートの伺う事項・順序の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>令和8年10月上旬（本打合せの後）</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>3町合同</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>意見交換会。3町共通の確認事項と地域課題。別冊「3町合同意見交換会資料」による</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>令和8年10月中旬から下旬</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>町ごと</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>町別ヒアリング。04シートの1の事項を町ごとに伺う</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>令和8年10月30日</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>広域連合</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量 第2次概算の提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>令和8年11月13日</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>広域連合</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>予算編成用の数値の提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>令和8年11月</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>広域連合・3町</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>3町の意見の反映と計画の骨子の整理</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2　お持ちする資料（いずれも既にお送りしているもの）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>資料</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>使う場面</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>別冊「3町ヒアリング資料」</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>ヒアリング本体</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>伺う事項と当方の整理を章立てで示したもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>別冊「キックオフ会議ヒアリングシート」</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ヒアリング本体</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>伺った内容をその場で書き留める記録の用紙</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>別冊「3町別の論点整理」</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>ヒアリング本体</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>町ごとの現在地と論点、3町共通の論点、協議の進め方</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>別冊「10月 地域課題の整理と3町協議の確認事項」</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>ヒアリング本体</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>地域課題15件と、町ごとの確認事項（町別の3シート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>別冊「3町合同意見交換会資料」</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>3町合同の意見交換会</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>策定の状況・第1次概算の結果・月額を動かす前提・地域課題15件・3町共通の確認事項・認知症施策推進計画・10月以降の工程</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>別冊「町別データシート」</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>町へお示しするもの</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>町ごとの人口・認定者数・サービスの利用状況・総合事業</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>別冊「交付金 市町村分評価指標と3町の評価」</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>町へお示しするもの</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>評価指標の大項目と明細列ごとの3町の得点</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>別冊「交付金評価の取りまとめと第10期への反映」</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>町へお示しするもの</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>3か年の推移、全国との比較、一部の町のみ得点している項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>別冊「サービス見込量の算定_第2次概算」</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>協議の前提</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>第1次概算からの差分と、月額を動かす前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>別冊「資料を受領できない場合のサービス見込量」</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>協議の前提</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>資料のご提供がない場合に確定する値と、確定しない値</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>注）上記は「3町ヒアリング・打合せ資料一式」として束ねたものに収めています。索引に、どれをどの場面で開くかを1行ずつ付しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>3　町別データシートをお示しする際の留意</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="130" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>・町別データシートの数値は計画作成支援ツールによるもので、3町を足しても広域連合の実績（介護保険事業状況報告）の値になりません。区域外の施設を利用する当連合の被保険者と、区域内の施設を利用する他の保険者の被保険者の扱いが違うためです（施設・居住系の月平均利用者数は3町計527人に対し保険者単位480.17人）。
+・サービス見込量・給付費・保険料は保険者（広域連合）を単位として算定するもので、町別には算定しません。町別に掲げるのは実績（人口・認定者数・給付費・事業所・総合事業・交付金の得点）です。
+・将来推計を町別に掲げるかは確認事項No.152のご判断によります（令和8年9月10日のご了承では、町別は現況のみを計画本文に加え、将来推計は3町計のままとしています）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>4　ヒアリングの場で踏み込まないこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="110" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>・保険料の額は3町計の概算までをお示しします。町別への按分は広域連合の規約によるものであり、当方に案はありません。
+・他の団体の名は協議の場に限ります。交付金の比較に用いている団体名は計画本文には掲げません。
+・得点が0である項目について、「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できません。評価調書によるご確認をお願いします。
+・第10期の施策に位置づけるかどうかは取組の必要性から判断するもので、交付金の得点のみを理由とはしません。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A13:D13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4159,7 +5196,7 @@
           <t>No.1〜No.177／177件／重複 なし</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4184,7 +5221,7 @@
           <t>未決164件／仮置きのないもの なし</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4196,12 +5233,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>02シートと03シートで同じ確認事項を二重に掲げていないこと</t>
+          <t>03シートと04シートで同じ確認事項を二重に掲げていないこと</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>02（確認先に町を含まない）と03（町を含む）の積集合</t>
+          <t>確認先に町を含まないものと含むものの積集合</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -4209,7 +5246,7 @@
           <t>重なり なし</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4221,7 +5258,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>02シートが点の高い順に並んでいること</t>
+          <t>03シートが点の高い順に並んでいること</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -4231,10 +5268,10 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>18件／降順 適合</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
+          <t>19件／降順 適合</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4246,20 +5283,20 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>02シートの絞り込みの条件を満たしていること</t>
+          <t>03シートの絞り込みの条件を満たしていること</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>確認先に町を含まず、点が4点以上</t>
+          <t>確認先に町を含まず、点が4点以上又はA群・B群に挙げたもの</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>18件（最小の点 4）</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
+          <t>19件（うち点が4点未満のもの [174]）</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4284,7 +5321,7 @@
           <t>11件（東川4・美瑛5・東神楽2）</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4309,7 +5346,7 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4321,20 +5358,20 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>04シートの件数が据え置きの区分B・Cの件数と一致すること</t>
+          <t>05シートの件数が据え置きの区分B・Cの件数と一致すること</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>区分B＋区分C ＝ 04シートの行数</t>
+          <t>区分B＋区分C ＝ 05シートの行数</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>19件／04シート 19件</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
+          <t>19件／05シート 19件</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4342,24 +5379,24 @@
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="5" t="n">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>算定上の月額基準額が百円未満四捨五入で6,400円になること</t>
+          <t>A群・B群に挙げた確認事項がいずれも未決であること</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>算定上の月額 6438.26円 → 基準額</t>
+          <t>A群・B群のNo. ⊆ 未決の確認事項</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>6,400円</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
+          <t>A群15件・B群6件／未決でないもの なし</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4367,24 +5404,24 @@
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>算定上の月額が算定の値と一致すること</t>
+          <t>A群とB群で同じ確認事項を二重に挙げていないこと</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>保険料収納必要額 ÷ 予定収納率 ÷ 補正後被保険者数 ÷ 12</t>
+          <t>A群のNo. ∩ B群のNo.</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>6438.2557円（算定 6438.2557円）</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
+          <t>重なり なし</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4392,24 +5429,24 @@
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="5" t="n">
-        <v>11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>総給付費が3か年の和になっていること</t>
+          <t>A群・B群の全件に決まらない場合の扱い（仮置き）があること</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>令和9・10・11年度の和</t>
+          <t>A群・B群のNo. ⊆ 既定値</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>9,035,114,142円</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
+          <t>実数21件／仮置きのないもの なし</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4417,24 +5454,24 @@
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>月額への効きとして総額を拾っていないこと</t>
+          <t>A群が4つの観点のうち2つ以上に当たること</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>1件の効きが2,000円を超えないこと</t>
+          <t>観点の記号を数える</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>最大327円</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
+          <t>5件／2つ未満のもの なし</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4442,24 +5479,24 @@
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="5" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>禁止表現が本資料にないこと</t>
+          <t>時間配分の案の合計が枠に収まっていること</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>禁止表現5件を全てのセルで探す</t>
+          <t>90分の案・120分の案のそれぞれの合計</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>0件</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
+          <t>90分の案 90分／120分の案 120分</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4467,24 +5504,24 @@
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>受託者の内部の仕組み・作業経過の語がないこと</t>
+          <t>A群の所要の合計が90分の案に組み込まれた分と一致すること</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>11語を全てのセルで探す</t>
+          <t>A群の分の和 ＝ 90分の案のA群の行の分</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>0件</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
+          <t>A群 55分／90分の案 55分</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4492,24 +5529,24 @@
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="5" t="n">
-        <v>15</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>個人情報の形（電話番号・メールアドレス）がないこと</t>
+          <t>A群の確認事項がいずれかの一覧（広域連合で決まるもの又は3町へ伺うもの）に掲げられていること</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>値の形で探す</t>
+          <t>A群のNo. ⊆ 03シート ∪ 04シート</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>0件</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
+          <t>A群15件／どちらにもないもの なし</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4517,24 +5554,24 @@
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>他の団体の固有名称がないこと</t>
+          <t>算定上の月額基準額が百円未満四捨五入で6,400円になること</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>全国集計から読んだ団体名247件を全てのセルで探す</t>
+          <t>算定上の月額 6438.26円 → 基準額</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>0件</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
+          <t>6,400円</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4542,24 +5579,24 @@
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>強調の記号が本文に残っていないこと</t>
+          <t>算定上の月額が算定の値と一致すること</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> を全てのセルで探す（書き出しの時点で落としている）</t>
+          <t>保険料収納必要額 ÷ 予定収納率 ÷ 補正後被保険者数 ÷ 12</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>0件</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
+          <t>6438.2557円（算定 6438.2557円）</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4567,24 +5604,199 @@
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>総給付費が3か年の和になっていること</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>令和9・10・11年度の和</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>9,035,114,142円</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>月額への効きとして総額を拾っていないこと</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>1件の効きが2,000円を超えないこと</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>最大327円</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>禁止表現が本資料にないこと</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>禁止表現5件を全てのセルで探す</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>受託者の内部の仕組み・作業経過の語がないこと</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>11語を全てのセルで探す</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>個人情報の形（電話番号・メールアドレス）がないこと</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>値の形で探す</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>他の団体の固有名称がないこと</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>全国集計から読んだ団体名247件を全てのセルで探す</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>強調の記号が本文に残っていないこと</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> を全てのセルで探す（書き出しの時点で落としている）</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>許容する文字の外の文字がないこと</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>日本語・英数字・定めた記号以外の文字を探す</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>0件</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>

--- a/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
+++ b/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
@@ -1633,7 +1633,7 @@
           <t>・A群・B群に挙げた確認事項は実数21件です。残る143件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
 ・このうち国の告示・公布を待つもの（据え置きの区分C）4件はこの場でお決めいただくことができません。介護報酬改定率・第1号被保険者負担割合・所得段階の政令改正・令和9年4月新設の3区分です。告示・公布の後に再算定します。
 ・受託者の側で確定できるもの（区分A）は残っていません。令和8年10月1日に4件（要介護度別の単価・1人1月あたり利用回（日）数・要介護度の構成・季節補正）を確定しました。
-・仮置きのまま計画素案へ反映した事項は46件あります（別冊「3町合同意見交換会資料」第6節3に一覧があります）。いずれもご決定をお待ちしているものであり、ご否認があれば素案の側を改めます。</t>
+・仮置きのまま計画素案へ反映した事項は62件あります（別冊「3町合同意見交換会資料」第6節3に一覧があります）。いずれもご決定をお待ちしているものであり、ご否認があれば素案の側を改めます。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
+++ b/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
@@ -1633,7 +1633,7 @@
           <t>・A群・B群に挙げた確認事項は実数21件です。残る143件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
 ・このうち国の告示・公布を待つもの（据え置きの区分C）4件はこの場でお決めいただくことができません。介護報酬改定率・第1号被保険者負担割合・所得段階の政令改正・令和9年4月新設の3区分です。告示・公布の後に再算定します。
 ・受託者の側で確定できるもの（区分A）は残っていません。令和8年10月1日に4件（要介護度別の単価・1人1月あたり利用回（日）数・要介護度の構成・季節補正）を確定しました。
-・仮置きのまま計画素案へ反映した事項は62件あります（別冊「3町合同意見交換会資料」第6節3に一覧があります）。いずれもご決定をお待ちしているものであり、ご否認があれば素案の側を改めます。</t>
+・仮置きのまま計画素案へ反映した事項は164件あります（別冊「3町合同意見交換会資料」第7節「受託者が仮置きにより進めた事項」に一覧があります）。いずれもご決定をお待ちしているものであり、ご否認があれば素案の側を改めます。</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>の当方の扱い＝案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
+          <t>案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>の当方の扱い＝国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
+          <t>国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
+++ b/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
@@ -620,7 +620,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月7日。</t>
+          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月14日。</t>
         </is>
       </c>
     </row>
@@ -761,11 +761,11 @@
     <row r="13" ht="180" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>・完了していない確認事項は164件あります。そのまま並べると一覧として用をなさないため、この場で決めるものは01シートのA群5件（計55分）に絞っています。
+          <t>・完了していない確認事項は168件あります。そのまま並べると一覧として用をなさないため、この場で決めるものは01シートのA群5件（計55分）に絞っています。
 ・03シートは「確認先が広域連合であり、影響度の点が4点以上のもの」に絞って19件を掲げています（A群・B群に挙げたものは点が下限に届かなくても掲げています）。A群はこの中から選んでいます（03シートに含まれないものは確認先に構成町を含むものです）。
-・04シートは確認先に構成町を含むもの37件です（町別11件・3町共通26件）。
+・04シートは確認先に構成町を含むもの40件です（町別11件・3町共通29件）。
 ・影響度の点は、期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで付けています。付け方は別冊「日次の状況と翌日の作業順位」と同じです。
-・決まらない場合の当方の扱い（仮置き）は164件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
+・決まらない場合の当方の扱い（仮置き）は168件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>打合せの時間が1〜2時間であることを踏まえ、完了していない確認事項164件のうち、この場で決めるものをA群5件（計55分）に絞りました。B群4件（計20分）は時間があれば、残りは決まらない場合の当方の扱い（仮置き）のまま進めます。</t>
+          <t>打合せの時間が1〜2時間であることを踏まえ、完了していない確認事項168件のうち、この場で決めるものをA群5件（計55分）に絞りました。B群4件（計20分）は時間があれば、残りは決まらない場合の当方の扱い（仮置き）のまま進めます。</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
     <row r="47" ht="130" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>・A群・B群に挙げた確認事項は実数21件です。残る143件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
+          <t>・A群・B群に挙げた確認事項は実数21件です。残る147件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
 ・このうち国の告示・公布を待つもの（据え置きの区分C）4件はこの場でお決めいただくことができません。介護報酬改定率・第1号被保険者負担割合・所得段階の政令改正・令和9年4月新設の3区分です。告示・公布の後に再算定します。
 ・受託者の側で確定できるもの（区分A）は残っていません。令和8年10月1日に4件（要介護度別の単価・1人1月あたり利用回（日）数・要介護度の構成・季節補正）を確定しました。
 ・仮置きのまま計画素案へ反映した事項は164件あります（別冊「3町合同意見交換会資料」第7節「受託者が仮置きにより進めた事項」に一覧があります）。いずれもご決定をお待ちしているものであり、ご否認があれば素案の側を改めます。</t>
@@ -2690,7 +2690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2711,7 +2711,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認先に構成町を含む確認事項37件（町別11件・3町共通26件）と、町からご提供をお願いする資料4件です。町別は町ごとに、3町共通は点の高い順に並べています。</t>
+          <t>確認先に構成町を含む確認事項40件（町別11件・3町共通29件）と、町からご提供をお願いする資料4件です。町別は町ごとに、3町共通は点の高い順に並べています。</t>
         </is>
       </c>
     </row>
@@ -3838,160 +3838,244 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="47" ht="46" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>178</v>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="46" customHeight="1">
+      <c r="A48" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>179</v>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>同計画は構成3町が定めるものとして計画素案に記載し、本計画は介護保険法第117条第3項による権利擁護の施策（第5章 基本目標1）をもって接続する。中核機関の整備の状況は［要確認］として残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="46" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>対象施設及び作成の状況を［要確認］として残し、第5章 基本目標5の主な事業に作成及び避難訓練の確認を置くにとどめ、達成目標に数値を掲げない。避難確保計画はBCPとは別の計画であり、BCPの策定率をもって作成の状況としない</t>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>3　町からご提供をお願いする資料</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>入手先</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>希望時期</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>何が確定するか</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="46" customHeight="1">
-      <c r="A50" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B50" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>3町</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="46" customHeight="1">
-      <c r="A51" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>総務省・3町</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>公表後</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>世帯構成の現状</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="46" customHeight="1">
-      <c r="A52" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>事業所・施設の定員と稼働の実績</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
         </is>
       </c>
     </row>
     <row r="53" ht="46" customHeight="1">
       <c r="A53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>3町</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="46" customHeight="1">
+      <c r="A54" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B53" s="5" t="n">
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>総務省・3町</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>公表後</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>世帯構成の現状</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="46" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>事業所・施設の定員と稼働の実績</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="46" customHeight="1">
+      <c r="A56" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>美瑛町・3町</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="48" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="57" ht="48" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>注）資料のご提供がない場合は、現に確認できている値で確定し、出所と制約を計画本文の注記に書く扱いとしています。算定そのものが止まるものはありません。</t>
         </is>
@@ -4000,12 +4084,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A51:F51"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A57:F57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5193,7 +5277,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>No.1〜No.177／177件／重複 なし</t>
+          <t>No.1〜No.181／181件／重複 なし</t>
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
@@ -5218,7 +5302,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>未決164件／仮置きのないもの なし</t>
+          <t>未決168件／仮置きのないもの なし</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">

--- a/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
+++ b/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
@@ -761,11 +761,11 @@
     <row r="13" ht="180" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>・完了していない確認事項は168件あります。そのまま並べると一覧として用をなさないため、この場で決めるものは01シートのA群5件（計55分）に絞っています。
+          <t>・完了していない確認事項は171件あります。そのまま並べると一覧として用をなさないため、この場で決めるものは01シートのA群5件（計55分）に絞っています。
 ・03シートは「確認先が広域連合であり、影響度の点が4点以上のもの」に絞って19件を掲げています（A群・B群に挙げたものは点が下限に届かなくても掲げています）。A群はこの中から選んでいます（03シートに含まれないものは確認先に構成町を含むものです）。
-・04シートは確認先に構成町を含むもの40件です（町別11件・3町共通29件）。
+・04シートは確認先に構成町を含むもの41件です（町別11件・3町共通30件）。
 ・影響度の点は、期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで付けています。付け方は別冊「日次の状況と翌日の作業順位」と同じです。
-・決まらない場合の当方の扱い（仮置き）は168件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
+・決まらない場合の当方の扱い（仮置き）は171件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>打合せの時間が1〜2時間であることを踏まえ、完了していない確認事項168件のうち、この場で決めるものをA群5件（計55分）に絞りました。B群4件（計20分）は時間があれば、残りは決まらない場合の当方の扱い（仮置き）のまま進めます。</t>
+          <t>打合せの時間が1〜2時間であることを踏まえ、完了していない確認事項171件のうち、この場で決めるものをA群5件（計55分）に絞りました。B群4件（計20分）は時間があれば、残りは決まらない場合の当方の扱い（仮置き）のまま進めます。</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
     <row r="47" ht="130" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>・A群・B群に挙げた確認事項は実数21件です。残る147件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
+          <t>・A群・B群に挙げた確認事項は実数21件です。残る150件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
 ・このうち国の告示・公布を待つもの（据え置きの区分C）4件はこの場でお決めいただくことができません。介護報酬改定率・第1号被保険者負担割合・所得段階の政令改正・令和9年4月新設の3区分です。告示・公布の後に再算定します。
 ・受託者の側で確定できるもの（区分A）は残っていません。令和8年10月1日に4件（要介護度別の単価・1人1月あたり利用回（日）数・要介護度の構成・季節補正）を確定しました。
 ・仮置きのまま計画素案へ反映した事項は164件あります（別冊「3町合同意見交換会資料」第7節「受託者が仮置きにより進めた事項」に一覧があります）。いずれもご決定をお待ちしているものであり、ご否認があれば素案の側を改めます。</t>
@@ -2690,7 +2690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2711,7 +2711,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認先に構成町を含む確認事項40件（町別11件・3町共通29件）と、町からご提供をお願いする資料4件です。町別は町ごとに、3町共通は点の高い順に並べています。</t>
+          <t>確認先に構成町を含む確認事項41件（町別11件・3町共通30件）と、町からご提供をお願いする資料4件です。町別は町ごとに、3町共通は点の高い順に並べています。</t>
         </is>
       </c>
     </row>
@@ -3922,160 +3922,188 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="50" ht="46" customHeight="1">
+      <c r="A50" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>184</v>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町・事業者</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>R8.12</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>令和7年度（12か月の完結年度）の実績により短期入所生活介護の見込量を算定し、季節補正を行わない（基準年度が完結年度であるため年度換算係数は1.0000となり効きは0円である）。季節利用の例外が示された時点で利用日数の置き方を確かめる</t>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>3　町からご提供をお願いする資料</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>入手先</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>希望時期</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>何が確定するか</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="46" customHeight="1">
-      <c r="A53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>3町</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
     </row>
     <row r="54" ht="46" customHeight="1">
       <c r="A54" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>総務省・3町</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>公表後</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>世帯構成の現状</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
     </row>
     <row r="55" ht="46" customHeight="1">
       <c r="A55" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>総務省・3町</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>公表後</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>世帯構成の現状</t>
         </is>
       </c>
     </row>
     <row r="56" ht="46" customHeight="1">
       <c r="A56" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>事業所・施設の定員と稼働の実績</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="46" customHeight="1">
+      <c r="A57" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B56" s="5" t="n">
+      <c r="B57" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>美瑛町・3町</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="48" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58" ht="48" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>注）資料のご提供がない場合は、現に確認できている値で確定し、出所と制約を計画本文の注記に書く扱いとしています。算定そのものが止まるものはありません。</t>
         </is>
@@ -4084,12 +4112,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A52:F52"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A58:F58"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A57:F57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5277,7 +5305,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>No.1〜No.181／181件／重複 なし</t>
+          <t>No.1〜No.184／184件／重複 なし</t>
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
@@ -5302,7 +5330,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>未決168件／仮置きのないもの なし</t>
+          <t>未決171件／仮置きのないもの なし</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">

--- a/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
+++ b/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
@@ -620,7 +620,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月14日。</t>
+          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月15日。</t>
         </is>
       </c>
     </row>
@@ -761,11 +761,11 @@
     <row r="13" ht="180" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>・完了していない確認事項は171件あります。そのまま並べると一覧として用をなさないため、この場で決めるものは01シートのA群5件（計55分）に絞っています。
+          <t>・完了していない確認事項は173件あります。そのまま並べると一覧として用をなさないため、この場で決めるものは01シートのA群5件（計55分）に絞っています。
 ・03シートは「確認先が広域連合であり、影響度の点が4点以上のもの」に絞って19件を掲げています（A群・B群に挙げたものは点が下限に届かなくても掲げています）。A群はこの中から選んでいます（03シートに含まれないものは確認先に構成町を含むものです）。
-・04シートは確認先に構成町を含むもの41件です（町別11件・3町共通30件）。
+・04シートは確認先に構成町を含むもの42件です（町別11件・3町共通31件）。
 ・影響度の点は、期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで付けています。付け方は別冊「日次の状況と翌日の作業順位」と同じです。
-・決まらない場合の当方の扱い（仮置き）は171件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
+・決まらない場合の当方の扱い（仮置き）は173件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>打合せの時間が1〜2時間であることを踏まえ、完了していない確認事項171件のうち、この場で決めるものをA群5件（計55分）に絞りました。B群4件（計20分）は時間があれば、残りは決まらない場合の当方の扱い（仮置き）のまま進めます。</t>
+          <t>打合せの時間が1〜2時間であることを踏まえ、完了していない確認事項173件のうち、この場で決めるものをA群5件（計55分）に絞りました。B群4件（計20分）は時間があれば、残りは決まらない場合の当方の扱い（仮置き）のまま進めます。</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
     <row r="47" ht="130" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>・A群・B群に挙げた確認事項は実数21件です。残る150件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
+          <t>・A群・B群に挙げた確認事項は実数21件です。残る152件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
 ・このうち国の告示・公布を待つもの（据え置きの区分C）4件はこの場でお決めいただくことができません。介護報酬改定率・第1号被保険者負担割合・所得段階の政令改正・令和9年4月新設の3区分です。告示・公布の後に再算定します。
 ・受託者の側で確定できるもの（区分A）は残っていません。令和8年10月1日に4件（要介護度別の単価・1人1月あたり利用回（日）数・要介護度の構成・季節補正）を確定しました。
 ・仮置きのまま計画素案へ反映した事項は164件あります（別冊「3町合同意見交換会資料」第7節「受託者が仮置きにより進めた事項」に一覧があります）。いずれもご決定をお待ちしているものであり、ご否認があれば素案の側を改めます。</t>
@@ -2690,7 +2690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2711,7 +2711,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認先に構成町を含む確認事項41件（町別11件・3町共通30件）と、町からご提供をお願いする資料4件です。町別は町ごとに、3町共通は点の高い順に並べています。</t>
+          <t>確認先に構成町を含む確認事項42件（町別11件・3町共通31件）と、町からご提供をお願いする資料4件です。町別は町ごとに、3町共通は点の高い順に並べています。</t>
         </is>
       </c>
     </row>
@@ -3950,160 +3950,188 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+    <row r="51" ht="46" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>185</v>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>R8.12</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す</t>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>3　町からご提供をお願いする資料</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>入手先</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>希望時期</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>何が確定するか</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="46" customHeight="1">
-      <c r="A54" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>3町</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
     </row>
     <row r="55" ht="46" customHeight="1">
       <c r="A55" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>総務省・3町</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>公表後</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>世帯構成の現状</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
     </row>
     <row r="56" ht="46" customHeight="1">
       <c r="A56" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>総務省・3町</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>公表後</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>世帯構成の現状</t>
         </is>
       </c>
     </row>
     <row r="57" ht="46" customHeight="1">
       <c r="A57" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>事業所・施設の定員と稼働の実績</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="46" customHeight="1">
+      <c r="A58" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B57" s="5" t="n">
+      <c r="B58" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>美瑛町・3町</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="48" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59" ht="48" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>注）資料のご提供がない場合は、現に確認できている値で確定し、出所と制約を計画本文の注記に書く扱いとしています。算定そのものが止まるものはありません。</t>
         </is>
@@ -4112,12 +4140,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A52:F52"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A58:F58"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A59:F59"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5305,7 +5333,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>No.1〜No.184／184件／重複 なし</t>
+          <t>No.1〜No.186／186件／重複 なし</t>
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
@@ -5330,7 +5358,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>未決171件／仮置きのないもの なし</t>
+          <t>未決173件／仮置きのないもの なし</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">

--- a/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
+++ b/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
@@ -761,11 +761,11 @@
     <row r="13" ht="180" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>・完了していない確認事項は173件あります。そのまま並べると一覧として用をなさないため、この場で決めるものは01シートのA群5件（計55分）に絞っています。
+          <t>・完了していない確認事項は172件あります。そのまま並べると一覧として用をなさないため、この場で決めるものは01シートのA群5件（計55分）に絞っています。
 ・03シートは「確認先が広域連合であり、影響度の点が4点以上のもの」に絞って19件を掲げています（A群・B群に挙げたものは点が下限に届かなくても掲げています）。A群はこの中から選んでいます（03シートに含まれないものは確認先に構成町を含むものです）。
 ・04シートは確認先に構成町を含むもの42件です（町別11件・3町共通31件）。
 ・影響度の点は、期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで付けています。付け方は別冊「日次の状況と翌日の作業順位」と同じです。
-・決まらない場合の当方の扱い（仮置き）は173件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
+・決まらない場合の当方の扱い（仮置き）は172件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>打合せの時間が1〜2時間であることを踏まえ、完了していない確認事項173件のうち、この場で決めるものをA群5件（計55分）に絞りました。B群4件（計20分）は時間があれば、残りは決まらない場合の当方の扱い（仮置き）のまま進めます。</t>
+          <t>打合せの時間が1〜2時間であることを踏まえ、完了していない確認事項172件のうち、この場で決めるものをA群5件（計55分）に絞りました。B群4件（計20分）は時間があれば、残りは決まらない場合の当方の扱い（仮置き）のまま進めます。</t>
         </is>
       </c>
     </row>
@@ -1630,10 +1630,10 @@
     <row r="47" ht="130" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>・A群・B群に挙げた確認事項は実数21件です。残る152件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
+          <t>・A群・B群に挙げた確認事項は実数21件です。残る151件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
 ・このうち国の告示・公布を待つもの（据え置きの区分C）4件はこの場でお決めいただくことができません。介護報酬改定率・第1号被保険者負担割合・所得段階の政令改正・令和9年4月新設の3区分です。告示・公布の後に再算定します。
 ・受託者の側で確定できるもの（区分A）は残っていません。令和8年10月1日に4件（要介護度別の単価・1人1月あたり利用回（日）数・要介護度の構成・季節補正）を確定しました。
-・仮置きのまま計画素案へ反映した事項は164件あります（別冊「3町合同意見交換会資料」第7節「受託者が仮置きにより進めた事項」に一覧があります）。いずれもご決定をお待ちしているものであり、ご否認があれば素案の側を改めます。</t>
+・仮置きのまま計画素案へ反映した事項は163件あります（別冊「3町合同意見交換会資料」第7節「受託者が仮置きにより進めた事項」に一覧があります）。いずれもご決定をお待ちしているものであり、ご否認があれば素案の側を改めます。</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す</t>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>未決173件／仮置きのないもの なし</t>
+          <t>未決172件／仮置きのないもの なし</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">

--- a/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
+++ b/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
@@ -761,11 +761,11 @@
     <row r="13" ht="180" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>・完了していない確認事項は172件あります。そのまま並べると一覧として用をなさないため、この場で決めるものは01シートのA群5件（計55分）に絞っています。
-・03シートは「確認先が広域連合であり、影響度の点が4点以上のもの」に絞って19件を掲げています（A群・B群に挙げたものは点が下限に届かなくても掲げています）。A群はこの中から選んでいます（03シートに含まれないものは確認先に構成町を含むものです）。
+          <t>・完了していない確認事項は173件あります。そのまま並べると一覧として用をなさないため、この場で決めるものは01シートのA群5件（計55分）に絞っています。
+・03シートは「確認先が広域連合であり、影響度の点が4点以上のもの」に絞って18件を掲げています（A群・B群に挙げたものは点が下限に届かなくても掲げています）。A群はこの中から選んでいます（03シートに含まれないものは確認先に構成町を含むものです）。
 ・04シートは確認先に構成町を含むもの42件です（町別11件・3町共通31件）。
 ・影響度の点は、期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで付けています。付け方は別冊「日次の状況と翌日の作業順位」と同じです。
-・決まらない場合の当方の扱い（仮置き）は172件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
+・決まらない場合の当方の扱い（仮置き）は173件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>打合せの時間が1〜2時間であることを踏まえ、完了していない確認事項172件のうち、この場で決めるものをA群5件（計55分）に絞りました。B群4件（計20分）は時間があれば、残りは決まらない場合の当方の扱い（仮置き）のまま進めます。</t>
+          <t>打合せの時間が1〜2時間であることを踏まえ、完了していない確認事項173件のうち、この場で決めるものをA群5件（計55分）に絞りました。B群4件（計20分）は時間があれば、残りは決まらない場合の当方の扱い（仮置き）のまま進めます。</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>No.88・No.113・No.84</t>
+          <t>No.88・No.84</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -1630,10 +1630,10 @@
     <row r="47" ht="130" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>・A群・B群に挙げた確認事項は実数21件です。残る151件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
+          <t>・A群・B群に挙げた確認事項は実数20件です。残る153件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
 ・このうち国の告示・公布を待つもの（据え置きの区分C）4件はこの場でお決めいただくことができません。介護報酬改定率・第1号被保険者負担割合・所得段階の政令改正・令和9年4月新設の3区分です。告示・公布の後に再算定します。
 ・受託者の側で確定できるもの（区分A）は残っていません。令和8年10月1日に4件（要介護度別の単価・1人1月あたり利用回（日）数・要介護度の構成・季節補正）を確定しました。
-・仮置きのまま計画素案へ反映した事項は163件あります（別冊「3町合同意見交換会資料」第7節「受託者が仮置きにより進めた事項」に一覧があります）。いずれもご決定をお待ちしているものであり、ご否認があれば素案の側を改めます。</t>
+・仮置きのまま計画素案へ反映した事項は162件あります（別冊「3町合同意見交換会資料」第7節「受託者が仮置きにより進めた事項」に一覧があります）。いずれもご決定をお待ちしているものであり、ご否認があれば素案の側を改めます。</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1965,7 +1965,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認先が広域連合であり、影響度の点が4点以上のもの（及びA群・B群に挙げたもの）19件です。点の高い順に並べています。「決まらない場合の当方の扱い」は仮置きであり、この打合せでご否認がなければそのまま第2次概算に用います。</t>
+          <t>確認先が広域連合であり、影響度の点が4点以上のもの（及びA群・B群に挙げたもの）18件です。点の高い順に並べています。「決まらない場合の当方の扱い」は仮置きであり、この打合せでご否認がなければそのまま第2次概算に用います。</t>
         </is>
       </c>
     </row>
@@ -2151,17 +2151,17 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めるか</t>
+          <t>第6章第2節の見込量の表に何を掲げるか</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定
-計画素案 第6章第4節4</t>
+          <t>計画素案 第6章第2節・第3節
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めないまま概算する</t>
+          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
         </is>
       </c>
     </row>
@@ -2185,22 +2185,23 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量の表に何を掲げるか</t>
+          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節・第3節
-サービス見込量の算定</t>
+          <t>サービス見込量 第2次概算
+将来推計 第3段階
+計画素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
@@ -2210,7 +2211,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
+          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
         </is>
       </c>
     </row>
@@ -2219,11 +2220,11 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -2245,7 +2246,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
+          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
         </is>
       </c>
     </row>
@@ -2254,18 +2255,18 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>令和22年度までの中長期推計をどこまで算定するか</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
           <t>サービス見込量 第2次概算
 将来推計 第3段階
-計画素案 第6章第3節・第6節</t>
+計画素案 第2章第8節・第6章第2節</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -2280,7 +2281,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
+          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
         </is>
       </c>
     </row>
@@ -2289,18 +2290,17 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>令和22年度までの中長期推計をどこまで算定するか</t>
+          <t>町別の人口の将来推計を計画本文に掲げるか</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
           <t>サービス見込量 第2次概算
-将来推計 第3段階
-計画素案 第2章第8節・第6章第2節</t>
+計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
+          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
         </is>
       </c>
     </row>
@@ -2324,11 +2324,11 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
+          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
         </is>
       </c>
     </row>
@@ -2358,22 +2358,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>153</v>
+        <v>7</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算
-計画素案 第2章第1節・第6章第1節</t>
+          <t>素案 第1章第6節・第3章第4節</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="F15" s="17" t="inlineStr">
@@ -2383,7 +2382,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
+          <t>第9期の自己評価と北海道への報告の実績を確認できないものとして、第10期の進行管理に自己評価の仕組みを置く</t>
         </is>
       </c>
     </row>
@@ -2392,16 +2391,17 @@
         <v>12</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>施策反映を行うか。行う場合の対象と歯止め</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第6節・第3章第4節</t>
+          <t>サービス見込量の算定
+計画素案 第4章第3節・第6章第2節</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>最大13円</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績を確認できないものとして、第10期の進行管理に自己評価の仕組みを置く</t>
+          <t>施策反映を行わないまま概算する（安全側）</t>
         </is>
       </c>
     </row>
@@ -2425,17 +2425,17 @@
         <v>13</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行うか。行う場合の対象と歯止め</t>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定
-計画素案 第4章第3節・第6章第2節</t>
+          <t>将来推計 第2段階
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2443,14 +2443,14 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>最大13円</t>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>最大327円</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行わないまま概算する（安全側）</t>
+          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
     </row>
@@ -2459,32 +2459,33 @@
         <v>14</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-サービス見込量の算定</t>
+          <t>計画素案 第6章第6節
+将来推計 第3段階
+保険料算定式の国の様式との対照</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>最大327円</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
+          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
         </is>
       </c>
     </row>
@@ -2493,18 +2494,17 @@
         <v>15</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
+          <t>給付適正化計画の位置づけ（案Bの採用）と毎年度の目標の記載場所</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第6節
-将来推計 第3段階
-保険料算定式の国の様式との対照</t>
+          <t>計画素案 第1章第2節・第5章 基本目標5・資料5
+給付適正化計画の位置づけと追加検討事項</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
+          <t>給付適正化計画の位置づけは案B（第9期と同じく施策として置き、施策名のかっこ書きで第7期給付適正化計画であることを示す）のままとする（令和8年9月10日 了承済み）</t>
         </is>
       </c>
     </row>
@@ -2528,17 +2528,17 @@
         <v>16</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけ（案Bの採用）と毎年度の目標の記載場所</t>
+          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第5章 基本目標5・資料5
-給付適正化計画の位置づけと追加検討事項</t>
+          <t>サービス見込量の算定
+計画素案 第5章 基本目標5・第6章第2節</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2546,14 +2546,14 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>最大327円</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけは案B（第9期と同じく施策として置き、施策名のかっこ書きで第7期給付適正化計画であることを示す）のままとする（令和8年9月10日 了承済み）</t>
+          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
         </is>
       </c>
     </row>
@@ -2562,32 +2562,32 @@
         <v>17</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
+          <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定
-計画素案 第5章 基本目標5・第6章第2節</t>
+          <t>第10期の段階設計
+保険料の算定</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>告示後</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>最大327円</t>
+          <t>最大290円</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
+          <t>第9期条例の16段階・乗率（公費軽減前）を据え置いて算定し、政令の公布後に再算定する</t>
         </is>
       </c>
     </row>
@@ -2596,75 +2596,41 @@
         <v>18</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>33</v>
+        <v>174</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階）</t>
+          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>第10期の段階設計
-保険料の算定</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>告示後</t>
-        </is>
-      </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>最大290円</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>第9期条例の16段階・乗率（公費軽減前）を据え置いて算定し、政令の公布後に再算定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>174</v>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>人口推計コーホート分析の妥当性検証 07シート
 見える化へ入力する箇所と入力値 02シート
 計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="170" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="23" ht="170" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>注1）この打合せで特にお決めいただきたいのは、01シートのA群5件（計55分）です。本シートの中では次のものが当たります。
-　A1　No.88・No.113・No.84　日常生活圏域と必要利用定員総数（基盤整備の単位）（15分）
+　A1　No.88・No.84　日常生活圏域と必要利用定員総数（基盤整備の単位）（15分）
 　A2　No.137・No.104・No.109・No.110　1人1月あたり給付費（単価）をどの年度で固定するか（15分）
 　A3　No.112・No.150　地域支援事業及び認知症総合支援事業の量の見込み（10分）
 　A4　No.152・No.153・No.174　人口の将来推計を案Cのままとするか（10分）
@@ -2676,9 +2642,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3862,7 +3828,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない</t>
+          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない【令和8年10月15日】参照条文により、介護保険法第117条第7項が「老人福祉法第20条の8第1項に規定する市町村老人福祉計画と一体のものとして作成されなければならない」ことを定めていることを確かめた。条及び項は第20条の8第1項である。老人福祉法そのものの条文は参照条文に収録されていない（第18条及び第20条の6のみ）ため、同条の内容及び市町村老人福祉計画の記載事項はなお確認できていない</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3940,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する</t>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する【令和8年10月15日】参照条文には社会福祉法第106条の3（包括的な支援体制の整備）までが収録されており、第106条の6は改正法により新設される規定であるため現れない。本件は進んでいない</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5299,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>No.1〜No.186／186件／重複 なし</t>
+          <t>No.1〜No.189／189件／重複 なし</t>
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
@@ -5358,7 +5324,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>未決172件／仮置きのないもの なし</t>
+          <t>未決173件／仮置きのないもの なし</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -5408,7 +5374,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>19件／降順 適合</t>
+          <t>18件／降順 適合</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -5433,7 +5399,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>19件（うち点が4点未満のもの [174]）</t>
+          <t>18件（うち点が4点未満のもの [174]）</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -5533,7 +5499,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>A群15件・B群6件／未決でないもの なし</t>
+          <t>A群14件・B群6件／未決でないもの なし</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -5583,7 +5549,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>実数21件／仮置きのないもの なし</t>
+          <t>実数20件／仮置きのないもの なし</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -5683,7 +5649,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>A群15件／どちらにもないもの なし</t>
+          <t>A群14件／どちらにもないもの なし</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">

--- a/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
+++ b/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
@@ -620,7 +620,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月15日。</t>
+          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月16日。</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
           <t>・A群・B群に挙げた確認事項は実数20件です。残る153件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
 ・このうち国の告示・公布を待つもの（据え置きの区分C）4件はこの場でお決めいただくことができません。介護報酬改定率・第1号被保険者負担割合・所得段階の政令改正・令和9年4月新設の3区分です。告示・公布の後に再算定します。
 ・受託者の側で確定できるもの（区分A）は残っていません。令和8年10月1日に4件（要介護度別の単価・1人1月あたり利用回（日）数・要介護度の構成・季節補正）を確定しました。
-・仮置きのまま計画素案へ反映した事項は162件あります（別冊「3町合同意見交換会資料」第7節「受託者が仮置きにより進めた事項」に一覧があります）。いずれもご決定をお待ちしているものであり、ご否認があれば素案の側を改めます。</t>
+・仮置きのまま計画素案へ反映した事項は171件あります（別冊「3町合同意見交換会資料」第7節「受託者が仮置きにより進めた事項」に一覧があります）。いずれもご決定をお待ちしているものであり、ご否認があれば素案の側を改めます。</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない【令和8年10月15日】参照条文により、介護保険法第117条第7項が「老人福祉法第20条の8第1項に規定する市町村老人福祉計画と一体のものとして作成されなければならない」ことを定めていることを確かめた。条及び項は第20条の8第1項である。老人福祉法そのものの条文は参照条文に収録されていない（第18条及び第20条の6のみ）ため、同条の内容及び市町村老人福祉計画の記載事項はなお確認できていない</t>
+          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する【令和8年10月15日】参照条文には社会福祉法第106条の3（包括的な支援体制の整備）までが収録されており、第106条の6は改正法により新設される規定であるため現れない。本件は進んでいない</t>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
+++ b/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
@@ -89,17 +89,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00DEEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -173,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -192,7 +192,10 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -200,7 +203,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -218,22 +221,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -601,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -620,7 +623,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月16日。</t>
+          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月19日。</t>
         </is>
       </c>
     </row>
@@ -769,12 +772,31 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>3　本資料の時点</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="118" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>・本資料は事前打合せ（令和8年10月8日）の時点の状況によるものです。確認事項の件数・状態・影響度の点はいずれもその時点のものです。
+・令和8年10月19日、ほぼ全ての確認事項について受託者案により作成を進めることをご了承いただきました。 これにより本資料に掲げた173件はいずれも受託者案で確定したものとして扱っています（確認事項として挙げた経緯は業務工程管理表に残しています）。A群・B群としてこの場でお決めいただきたいとしていた事項も、受託者案のとおり進めます。
+・残るのは、保険料に関わる国の政令・省令・告示の公布後に再算定する13件です。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -849,7 +871,7 @@
       </c>
     </row>
     <row r="6" ht="96" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
@@ -874,14 +896,14 @@
           <t>①③④</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>15分</t>
         </is>
       </c>
     </row>
     <row r="7" ht="96" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
@@ -906,14 +928,14 @@
           <t>②④</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>15分</t>
         </is>
       </c>
     </row>
     <row r="8" ht="96" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
@@ -938,14 +960,14 @@
           <t>①③④</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>10分</t>
         </is>
       </c>
     </row>
     <row r="9" ht="96" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
@@ -970,14 +992,14 @@
           <t>①④</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>10分</t>
         </is>
       </c>
     </row>
     <row r="10" ht="96" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>A5</t>
         </is>
@@ -1002,7 +1024,7 @@
           <t>②④</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>5分</t>
         </is>
@@ -1208,13 +1230,13 @@
           <t>内容</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n"/>
+      <c r="D22" s="11" t="n"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
           <t>A群で当たるもの</t>
         </is>
       </c>
-      <c r="F22" s="10" t="n"/>
+      <c r="F22" s="11" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -1232,13 +1254,13 @@
           <t>広域連合としての置き方が決まらないと、各町へ伺う問いが立たない</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n"/>
+      <c r="D23" s="11" t="n"/>
       <c r="E23" s="5" t="inlineStr">
         <is>
           <t>A1・A3・A4</t>
         </is>
       </c>
-      <c r="F23" s="10" t="n"/>
+      <c r="F23" s="11" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
@@ -1256,13 +1278,13 @@
           <t>保険料の月額を100円以上動かし得る</t>
         </is>
       </c>
-      <c r="D24" s="10" t="n"/>
+      <c r="D24" s="11" t="n"/>
       <c r="E24" s="5" t="inlineStr">
         <is>
           <t>A2・A5</t>
         </is>
       </c>
-      <c r="F24" s="10" t="n"/>
+      <c r="F24" s="11" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -1280,13 +1302,13 @@
           <t>介護保険法第117条が定める記載事項そのものである</t>
         </is>
       </c>
-      <c r="D25" s="10" t="n"/>
+      <c r="D25" s="11" t="n"/>
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t>A1・A3</t>
         </is>
       </c>
-      <c r="F25" s="10" t="n"/>
+      <c r="F25" s="11" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -1304,13 +1326,13 @@
           <t>令和8年10月30日に提示する算定の前提として要る</t>
         </is>
       </c>
-      <c r="D26" s="10" t="n"/>
+      <c r="D26" s="11" t="n"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
           <t>A1・A2・A3・A4・A5</t>
         </is>
       </c>
-      <c r="F26" s="10" t="n"/>
+      <c r="F26" s="11" t="n"/>
     </row>
     <row r="27" ht="48" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -1343,8 +1365,8 @@
           <t>内容</t>
         </is>
       </c>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="10" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="11" t="n"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
           <t>分</t>
@@ -1352,24 +1374,24 @@
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>90分</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>冒頭　仮置きによる算定の結果と、低く出る側に寄っていること（02シート）</t>
         </is>
       </c>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="13" t="inlineStr">
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>5分</t>
         </is>
@@ -1387,8 +1409,8 @@
           <t>A群　この場で決めること（5件・01シート）</t>
         </is>
       </c>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="10" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="11" t="n"/>
       <c r="F32" s="5" t="inlineStr">
         <is>
           <t>55分</t>
@@ -1407,8 +1429,8 @@
           <t>3町へ伺う事項と順序の確認（04シート）</t>
         </is>
       </c>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="10" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="11" t="n"/>
       <c r="F33" s="5" t="inlineStr">
         <is>
           <t>15分</t>
@@ -1427,8 +1449,8 @@
           <t>ヒアリングの進め方（日程・配付資料・記録の様式。06シート）</t>
         </is>
       </c>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="10" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="11" t="n"/>
       <c r="F34" s="5" t="inlineStr">
         <is>
           <t>10分</t>
@@ -1447,8 +1469,8 @@
           <t>予備</t>
         </is>
       </c>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="10" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="11" t="n"/>
       <c r="F35" s="5" t="inlineStr">
         <is>
           <t>5分</t>
@@ -1456,40 +1478,40 @@
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="15" t="inlineStr"/>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr"/>
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>90分</t>
         </is>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>120分</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C37" s="15" t="inlineStr">
         <is>
           <t>冒頭　仮置きによる算定の結果と、低く出る側に寄っていること（02シート）</t>
         </is>
       </c>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="13" t="inlineStr">
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>5分</t>
         </is>
@@ -1507,8 +1529,8 @@
           <t>A群　この場で決めること（5件・01シート）</t>
         </is>
       </c>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="10" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="11" t="n"/>
       <c r="F38" s="5" t="inlineStr">
         <is>
           <t>55分</t>
@@ -1527,8 +1549,8 @@
           <t>B群　時間があれば決めること（4件・01シート）</t>
         </is>
       </c>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="10" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="11" t="n"/>
       <c r="F39" s="5" t="inlineStr">
         <is>
           <t>20分</t>
@@ -1547,8 +1569,8 @@
           <t>3町へ伺う事項と順序の確認（04シート）</t>
         </is>
       </c>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="10" t="n"/>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="11" t="n"/>
       <c r="F40" s="5" t="inlineStr">
         <is>
           <t>20分</t>
@@ -1567,8 +1589,8 @@
           <t>ヒアリングの進め方（日程・配付資料・記録の様式。06シート）</t>
         </is>
       </c>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="10" t="n"/>
+      <c r="D41" s="12" t="n"/>
+      <c r="E41" s="11" t="n"/>
       <c r="F41" s="5" t="inlineStr">
         <is>
           <t>15分</t>
@@ -1587,8 +1609,8 @@
           <t>予備</t>
         </is>
       </c>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="10" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="11" t="n"/>
       <c r="F42" s="5" t="inlineStr">
         <is>
           <t>5分</t>
@@ -1596,16 +1618,16 @@
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="15" t="inlineStr"/>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr"/>
+      <c r="B43" s="17" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="C43" s="15" t="inlineStr"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="10" t="n"/>
-      <c r="F43" s="16" t="inlineStr">
+      <c r="C43" s="16" t="inlineStr"/>
+      <c r="D43" s="12" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="17" t="inlineStr">
         <is>
           <t>120分</t>
         </is>
@@ -1744,7 +1766,7 @@
           <t>総給付費（第10期3か年計）</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>9,035,114,142円</t>
         </is>
@@ -1764,7 +1786,7 @@
           <t>標準給付費見込額（A）</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>9,569,019,924円</t>
         </is>
@@ -1784,7 +1806,7 @@
           <t>地域支援事業費（B）</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>531,483,777円</t>
         </is>
@@ -1804,7 +1826,7 @@
           <t>保険料収納必要額（J）</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>2,088,171,801円</t>
         </is>
@@ -1824,7 +1846,7 @@
           <t>補正後第1号被保険者数（3か年）</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>27,301.2人</t>
         </is>
@@ -1844,7 +1866,7 @@
           <t>算定上の月額基準額</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>6,438.26円</t>
         </is>
@@ -1856,20 +1878,20 @@
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="13" t="n">
+      <c r="A12" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>保険料基準額（百円未満四捨五入）</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>6,400円</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>第9期の基準額6,400円と同額になります</t>
         </is>
@@ -2030,7 +2052,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>最大7円</t>
         </is>
@@ -2065,7 +2087,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2100,7 +2122,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>最大47円</t>
         </is>
@@ -2135,7 +2157,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>最大58円</t>
         </is>
@@ -2169,7 +2191,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2204,7 +2226,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2239,7 +2261,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2274,7 +2296,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2308,7 +2330,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2342,7 +2364,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2375,7 +2397,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2409,7 +2431,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>最大13円</t>
         </is>
@@ -2443,7 +2465,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>最大327円</t>
         </is>
@@ -2478,7 +2500,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2512,7 +2534,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2546,7 +2568,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>最大327円</t>
         </is>
@@ -2580,7 +2602,7 @@
           <t>告示後</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>最大290円</t>
         </is>
@@ -2615,7 +2637,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4181,7 +4203,7 @@
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -4196,7 +4218,7 @@
           <t>令和7年度の実績単価で固定した。改定率を乗じた場合の感度をサービス見込量の算定に示した</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>改定率1％あたり月額＋61円。単価の年率1.32％から1.75％の伸びを見込まないことは月額＋245円〜＋327円に当たり、令和8年度の水準（残差＋1.63％）に置くと月額＋99円（確認事項No.104）</t>
         </is>
@@ -4211,7 +4233,7 @@
       <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4226,7 +4248,7 @@
           <t>取崩しを行わない（I＝0）</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>1億円の取崩しで月額約▲310円</t>
         </is>
@@ -4241,7 +4263,7 @@
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -4256,7 +4278,7 @@
           <t>第9期と同じ23％で置いた</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>1ポイントの違いで月額が約290円動く</t>
         </is>
@@ -4271,7 +4293,7 @@
       <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4301,7 +4323,7 @@
       <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4331,7 +4353,7 @@
       <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4361,7 +4383,7 @@
       <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4391,7 +4413,7 @@
       <c r="A12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4421,7 +4443,7 @@
       <c r="A13" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4451,7 +4473,7 @@
       <c r="A14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4481,7 +4503,7 @@
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4511,7 +4533,7 @@
       <c r="A16" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4541,7 +4563,7 @@
       <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4571,7 +4593,7 @@
       <c r="A18" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -4601,7 +4623,7 @@
       <c r="A19" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -4631,7 +4653,7 @@
       <c r="A20" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4661,7 +4683,7 @@
       <c r="A21" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4691,7 +4713,7 @@
       <c r="A22" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4721,7 +4743,7 @@
       <c r="A23" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5302,7 +5324,7 @@
           <t>No.1〜No.189／189件／重複 なし</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5327,7 +5349,7 @@
           <t>未決173件／仮置きのないもの なし</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5352,7 +5374,7 @@
           <t>重なり なし</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5377,7 +5399,7 @@
           <t>18件／降順 適合</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5402,7 +5424,7 @@
           <t>18件（うち点が4点未満のもの [174]）</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5427,7 +5449,7 @@
           <t>11件（東川4・美瑛5・東神楽2）</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5452,7 +5474,7 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5477,7 +5499,7 @@
           <t>19件／05シート 19件</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5502,7 +5524,7 @@
           <t>A群14件・B群6件／未決でないもの なし</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5527,7 +5549,7 @@
           <t>重なり なし</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5552,7 +5574,7 @@
           <t>実数20件／仮置きのないもの なし</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5577,7 +5599,7 @@
           <t>5件／2つ未満のもの なし</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5602,7 +5624,7 @@
           <t>90分の案 90分／120分の案 120分</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5627,7 +5649,7 @@
           <t>A群 55分／90分の案 55分</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5652,7 +5674,7 @@
           <t>A群14件／どちらにもないもの なし</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5677,7 +5699,7 @@
           <t>6,400円</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5702,7 +5724,7 @@
           <t>6438.2557円（算定 6438.2557円）</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5727,7 +5749,7 @@
           <t>9,035,114,142円</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5752,7 +5774,7 @@
           <t>最大327円</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5777,7 +5799,7 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5802,7 +5824,7 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5827,7 +5849,7 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5852,7 +5874,7 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5877,7 +5899,7 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5902,7 +5924,7 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E29" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>

--- a/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
+++ b/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
@@ -764,11 +764,11 @@
     <row r="13" ht="180" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>・完了していない確認事項は173件あります。そのまま並べると一覧として用をなさないため、この場で決めるものは01シートのA群5件（計55分）に絞っています。
+          <t>・完了していない確認事項は174件あります。そのまま並べると一覧として用をなさないため、この場で決めるものは01シートのA群5件（計55分）に絞っています。
 ・03シートは「確認先が広域連合であり、影響度の点が4点以上のもの」に絞って18件を掲げています（A群・B群に挙げたものは点が下限に届かなくても掲げています）。A群はこの中から選んでいます（03シートに含まれないものは確認先に構成町を含むものです）。
 ・04シートは確認先に構成町を含むもの42件です（町別11件・3町共通31件）。
 ・影響度の点は、期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで付けています。付け方は別冊「日次の状況と翌日の作業順位」と同じです。
-・決まらない場合の当方の扱い（仮置き）は173件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
+・決まらない場合の当方の扱い（仮置き）は174件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>・本資料は事前打合せ（令和8年10月8日）の時点の状況によるものです。確認事項の件数・状態・影響度の点はいずれもその時点のものです。
-・令和8年10月19日、ほぼ全ての確認事項について受託者案により作成を進めることをご了承いただきました。 これにより本資料に掲げた173件はいずれも受託者案で確定したものとして扱っています（確認事項として挙げた経緯は業務工程管理表に残しています）。A群・B群としてこの場でお決めいただきたいとしていた事項も、受託者案のとおり進めます。
+・令和8年10月19日、ほぼ全ての確認事項について受託者案により作成を進めることをご了承いただきました。 これにより本資料に掲げた174件はいずれも受託者案で確定したものとして扱っています（確認事項として挙げた経緯は業務工程管理表に残しています）。A群・B群としてこの場でお決めいただきたいとしていた事項も、受託者案のとおり進めます。
 ・残るのは、保険料に関わる国の政令・省令・告示の公布後に再算定する13件です。</t>
         </is>
       </c>
@@ -830,7 +830,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>打合せの時間が1〜2時間であることを踏まえ、完了していない確認事項173件のうち、この場で決めるものをA群5件（計55分）に絞りました。B群4件（計20分）は時間があれば、残りは決まらない場合の当方の扱い（仮置き）のまま進めます。</t>
+          <t>打合せの時間が1〜2時間であることを踏まえ、完了していない確認事項174件のうち、この場で決めるものをA群5件（計55分）に絞りました。B群4件（計20分）は時間があれば、残りは決まらない場合の当方の扱い（仮置き）のまま進めます。</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
     <row r="47" ht="130" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>・A群・B群に挙げた確認事項は実数20件です。残る153件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
+          <t>・A群・B群に挙げた確認事項は実数20件です。残る154件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
 ・このうち国の告示・公布を待つもの（据え置きの区分C）4件はこの場でお決めいただくことができません。介護報酬改定率・第1号被保険者負担割合・所得段階の政令改正・令和9年4月新設の3区分です。告示・公布の後に再算定します。
 ・受託者の側で確定できるもの（区分A）は残っていません。令和8年10月1日に4件（要介護度別の単価・1人1月あたり利用回（日）数・要介護度の構成・季節補正）を確定しました。
 ・仮置きのまま計画素案へ反映した事項は171件あります（別冊「3町合同意見交換会資料」第7節「受託者が仮置きにより進めた事項」に一覧があります）。いずれもご決定をお待ちしているものであり、ご否認があれば素案の側を改めます。</t>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>No.1〜No.189／189件／重複 なし</t>
+          <t>No.1〜No.190／190件／重複 なし</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>未決173件／仮置きのないもの なし</t>
+          <t>未決174件／仮置きのないもの なし</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">

--- a/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
+++ b/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
@@ -623,7 +623,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月19日。</t>
+          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月20日。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
+++ b/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
@@ -623,7 +623,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月20日。</t>
+          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月21日。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
+++ b/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
@@ -623,7 +623,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月21日。</t>
+          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月23日。</t>
         </is>
       </c>
     </row>
@@ -764,11 +764,11 @@
     <row r="13" ht="180" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>・完了していない確認事項は174件あります。そのまま並べると一覧として用をなさないため、この場で決めるものは01シートのA群5件（計55分）に絞っています。
+          <t>・完了していない確認事項は176件あります。そのまま並べると一覧として用をなさないため、この場で決めるものは01シートのA群5件（計55分）に絞っています。
 ・03シートは「確認先が広域連合であり、影響度の点が4点以上のもの」に絞って18件を掲げています（A群・B群に挙げたものは点が下限に届かなくても掲げています）。A群はこの中から選んでいます（03シートに含まれないものは確認先に構成町を含むものです）。
 ・04シートは確認先に構成町を含むもの42件です（町別11件・3町共通31件）。
 ・影響度の点は、期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで付けています。付け方は別冊「日次の状況と翌日の作業順位」と同じです。
-・決まらない場合の当方の扱い（仮置き）は174件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
+・決まらない場合の当方の扱い（仮置き）は176件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>・本資料は事前打合せ（令和8年10月8日）の時点の状況によるものです。確認事項の件数・状態・影響度の点はいずれもその時点のものです。
-・令和8年10月19日、ほぼ全ての確認事項について受託者案により作成を進めることをご了承いただきました。 これにより本資料に掲げた174件はいずれも受託者案で確定したものとして扱っています（確認事項として挙げた経緯は業務工程管理表に残しています）。A群・B群としてこの場でお決めいただきたいとしていた事項も、受託者案のとおり進めます。
+・令和8年10月19日、ほぼ全ての確認事項について受託者案により作成を進めることをご了承いただきました。 これにより本資料に掲げた176件はいずれも受託者案で確定したものとして扱っています（確認事項として挙げた経緯は業務工程管理表に残しています）。A群・B群としてこの場でお決めいただきたいとしていた事項も、受託者案のとおり進めます。
 ・残るのは、保険料に関わる国の政令・省令・告示の公布後に再算定する13件です。</t>
         </is>
       </c>
@@ -830,7 +830,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>打合せの時間が1〜2時間であることを踏まえ、完了していない確認事項174件のうち、この場で決めるものをA群5件（計55分）に絞りました。B群4件（計20分）は時間があれば、残りは決まらない場合の当方の扱い（仮置き）のまま進めます。</t>
+          <t>打合せの時間が1〜2時間であることを踏まえ、完了していない確認事項176件のうち、この場で決めるものをA群5件（計55分）に絞りました。B群4件（計20分）は時間があれば、残りは決まらない場合の当方の扱い（仮置き）のまま進めます。</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
     <row r="47" ht="130" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>・A群・B群に挙げた確認事項は実数20件です。残る154件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
+          <t>・A群・B群に挙げた確認事項は実数20件です。残る156件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
 ・このうち国の告示・公布を待つもの（据え置きの区分C）4件はこの場でお決めいただくことができません。介護報酬改定率・第1号被保険者負担割合・所得段階の政令改正・令和9年4月新設の3区分です。告示・公布の後に再算定します。
 ・受託者の側で確定できるもの（区分A）は残っていません。令和8年10月1日に4件（要介護度別の単価・1人1月あたり利用回（日）数・要介護度の構成・季節補正）を確定しました。
 ・仮置きのまま計画素案へ反映した事項は171件あります（別冊「3町合同意見交換会資料」第7節「受託者が仮置きにより進めた事項」に一覧があります）。いずれもご決定をお待ちしているものであり、ご否認があれば素案の側を改めます。</t>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>No.1〜No.190／190件／重複 なし</t>
+          <t>No.1〜No.192／192件／重複 なし</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>未決174件／仮置きのないもの なし</t>
+          <t>未決176件／仮置きのないもの なし</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">

--- a/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
+++ b/output/第10期計画_ヒアリング前事前打合せ_確認事項.xlsx
@@ -623,7 +623,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月23日。</t>
+          <t>構成3町への町別ヒアリング（令和8年10月中旬から下旬）の前に、広域連合と受託者で行う事前打合せ（令和8年10月8日）でご確認・ご判断をお願いしたい事項をまとめたものです。ヒアリングの場で3町へ伺う事項は別冊「3町ヒアリング資料」及び別冊「10月 地域課題の整理と3町協議の確認事項」にあります。作成日 令和8年10月24日。</t>
         </is>
       </c>
     </row>
@@ -764,11 +764,11 @@
     <row r="13" ht="180" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>・完了していない確認事項は176件あります。そのまま並べると一覧として用をなさないため、この場で決めるものは01シートのA群5件（計55分）に絞っています。
+          <t>・完了していない確認事項は175件あります。そのまま並べると一覧として用をなさないため、この場で決めるものは01シートのA群5件（計55分）に絞っています。
 ・03シートは「確認先が広域連合であり、影響度の点が4点以上のもの」に絞って18件を掲げています（A群・B群に挙げたものは点が下限に届かなくても掲げています）。A群はこの中から選んでいます（03シートに含まれないものは確認先に構成町を含むものです）。
 ・04シートは確認先に構成町を含むもの42件です（町別11件・3町共通31件）。
 ・影響度の点は、期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで付けています。付け方は別冊「日次の状況と翌日の作業順位」と同じです。
-・決まらない場合の当方の扱い（仮置き）は176件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
+・決まらない場合の当方の扱い（仮置き）は175件すべてに置いています。このため、ご決定をお待ちしている事項があっても第2次概算（令和8年10月30日）は組めます。仮置きは協議を進めるためのものであり、公表の確定の根拠にはなりません。</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>・本資料は事前打合せ（令和8年10月8日）の時点の状況によるものです。確認事項の件数・状態・影響度の点はいずれもその時点のものです。
-・令和8年10月19日、ほぼ全ての確認事項について受託者案により作成を進めることをご了承いただきました。 これにより本資料に掲げた176件はいずれも受託者案で確定したものとして扱っています（確認事項として挙げた経緯は業務工程管理表に残しています）。A群・B群としてこの場でお決めいただきたいとしていた事項も、受託者案のとおり進めます。
+・令和8年10月19日、ほぼ全ての確認事項について受託者案により作成を進めることをご了承いただきました。 これにより本資料に掲げた175件はいずれも受託者案で確定したものとして扱っています（確認事項として挙げた経緯は業務工程管理表に残しています）。A群・B群としてこの場でお決めいただきたいとしていた事項も、受託者案のとおり進めます。
 ・残るのは、保険料に関わる国の政令・省令・告示の公布後に再算定する13件です。</t>
         </is>
       </c>
@@ -830,7 +830,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>打合せの時間が1〜2時間であることを踏まえ、完了していない確認事項176件のうち、この場で決めるものをA群5件（計55分）に絞りました。B群4件（計20分）は時間があれば、残りは決まらない場合の当方の扱い（仮置き）のまま進めます。</t>
+          <t>打合せの時間が1〜2時間であることを踏まえ、完了していない確認事項175件のうち、この場で決めるものをA群5件（計55分）に絞りました。B群4件（計20分）は時間があれば、残りは決まらない場合の当方の扱い（仮置き）のまま進めます。</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
     <row r="47" ht="130" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>・A群・B群に挙げた確認事項は実数20件です。残る156件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
+          <t>・A群・B群に挙げた確認事項は実数20件です。残る155件はこの場では扱わず、決まらない場合の当方の扱い（仮置き）のまま進めます。
 ・このうち国の告示・公布を待つもの（据え置きの区分C）4件はこの場でお決めいただくことができません。介護報酬改定率・第1号被保険者負担割合・所得段階の政令改正・令和9年4月新設の3区分です。告示・公布の後に再算定します。
 ・受託者の側で確定できるもの（区分A）は残っていません。令和8年10月1日に4件（要介護度別の単価・1人1月あたり利用回（日）数・要介護度の構成・季節補正）を確定しました。
 ・仮置きのまま計画素案へ反映した事項は171件あります（別冊「3町合同意見交換会資料」第7節「受託者が仮置きにより進めた事項」に一覧があります）。いずれもご決定をお待ちしているものであり、ご否認があれば素案の側を改めます。</t>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>No.1〜No.192／192件／重複 なし</t>
+          <t>No.1〜No.193／193件／重複 なし</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>未決176件／仮置きのないもの なし</t>
+          <t>未決175件／仮置きのないもの なし</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
